--- a/resources/print-on-demand/files/pod-int-margin-funnel.xlsx
+++ b/resources/print-on-demand/files/pod-int-margin-funnel.xlsx
@@ -17,11 +17,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0&quot;%&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,11 +73,6 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -104,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,8 +133,6 @@
     <xf numFmtId="1" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -505,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -527,7 +520,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -578,7 +570,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Platform fee %  (Etsy ~13 UK)</t>
+          <t>Platform fee %  (Etsy ~13 with Offsite Ads)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
@@ -598,11 +590,11 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Fixed fee per sale (Etsy UK ~0.43)</t>
+          <t>Fixed fee per sale (Etsy US ~0.45)</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +607,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -667,7 +658,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -688,7 +678,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Favourites</t>
+          <t>Favorites</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
@@ -708,7 +698,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Favourite rate</t>
+          <t>Favorite rate</t>
         </is>
       </c>
       <c r="B24" s="10">
@@ -736,7 +726,7 @@
     </row>
     <row r="27">
       <c r="A27" s="11">
-        <f>IF(B21&lt;200,"Discovery gap — too few views to judge; get it seen",IF(B23&gt;0,"Working — leave it",IF(B22/B21&lt;0.015,"Listing not landing — photo/title/offer/price","Friction at the till — price/shipping/reviews; investigate")))</f>
+        <f>IF(B21&lt;200,"Discovery gap — too few views to judge; get it seen",IF(B23&gt;0,"Working — leave it",IF(B22/B21&lt;0.015,"Listing not landing — photo/title/offer/price","Friction at checkout — price/shipping/reviews; investigate")))</f>
         <v/>
       </c>
     </row>
@@ -754,7 +744,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -765,17 +754,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Per-order fee saved per extra item (Etsy UK ~0.24)</t>
+          <t>Per-order fee saved per extra item (Etsy US ~0.25)</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Unit £</t>
+          <t>Unit $</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -791,7 +780,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="C34" s="14" t="n">
         <v>1</v>
@@ -804,13 +793,12 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="C35" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
@@ -847,11 +835,10 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Anchor: £4.41 + £1.59 = £6.00 apart, £6.24 together — a £0.24 lift.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+          <t>Anchor: $4.39 + $1.57 = $5.96 apart, $6.21 together — a $0.25 lift.</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
@@ -911,7 +898,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Anchor: 10% off the £16 mug cuts £1.59 to ~£0.20 (the fee drops too) —</t>
+          <t>Anchor: 10% off the $16 mug cuts $1.57 to ~$0.18 (the fee drops too) —</t>
         </is>
       </c>
     </row>
@@ -922,7 +909,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
@@ -936,10 +922,6 @@
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/print-on-demand/files/pod-int-margin-funnel.xlsx
+++ b/resources/print-on-demand/files/pod-int-margin-funnel.xlsx
@@ -919,7 +919,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
